--- a/event_registration_forms/020_stage_setup_payment_form--event_registration_forms.xlsx
+++ b/event_registration_forms/020_stage_setup_payment_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_user</t>
+          <t>assigned_user_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Assigned User</t>
+          <t>Assigned User 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>event_category</t>
+          <t>event_category_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Event Category</t>
+          <t>Event Category 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>service_status</t>
+          <t>service_status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Service Status</t>
+          <t>Service Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>service_type_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Service Type</t>
+          <t>Service Type 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>assigned_user_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,420 +1182,658 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>assigned_user_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>assigned_user_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>event_category_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>event_category_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>service_status_choices</t>
+          <t>event_category_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>service_status_choices</t>
+          <t>event_category_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>service_type_status_choices</t>
+          <t>event_category_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>service_type_status_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assigned_user_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>assigned_user_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>payment_terms_status_choices</t>
+          <t>service_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>payment_terms_status_choices</t>
+          <t>service_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>event_category_choices</t>
+          <t>service_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>event_category_choices</t>
+          <t>service_type_status_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>service_type_status_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>service_type_status_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>service_status_choices</t>
+          <t>assigned_user_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>service_status_choices</t>
+          <t>assigned_user_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>assigned_user_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>payment_terms_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>payment_terms_status_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>payment_terms_status_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>event_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>event_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>event_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>service_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>service_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>service_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>service_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>service_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>service_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
